--- a/artfynd/A 48985-2025 artfynd.xlsx
+++ b/artfynd/A 48985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129790469</v>
       </c>
       <c r="B2" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129790637</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129790513</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129790542</v>
       </c>
       <c r="B5" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129790558</v>
       </c>
       <c r="B6" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48985-2025 artfynd.xlsx
+++ b/artfynd/A 48985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129790469</v>
       </c>
       <c r="B2" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129790637</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129790513</v>
       </c>
       <c r="B4" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129790542</v>
       </c>
       <c r="B5" t="n">
-        <v>80217</v>
+        <v>80220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129790558</v>
       </c>
       <c r="B6" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48985-2025 artfynd.xlsx
+++ b/artfynd/A 48985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129790469</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129790513</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129790542</v>
       </c>
       <c r="B5" t="n">
-        <v>80220</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129790558</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48985-2025 artfynd.xlsx
+++ b/artfynd/A 48985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129790469</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129790637</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129790513</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129790542</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129790558</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48985-2025 artfynd.xlsx
+++ b/artfynd/A 48985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129790469</v>
       </c>
       <c r="B2" t="n">
-        <v>80201</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129790637</v>
+        <v>129790513</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lovarso Talltita, Dlr</t>
+          <t>Lovarso Skrovellav 2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467405</v>
+        <v>467375</v>
       </c>
       <c r="R3" t="n">
-        <v>6822149</v>
+        <v>6821924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +860,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre sumpig granskog vid Lovarsuonjoki (k-skog)</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129790513</v>
+        <v>129790558</v>
       </c>
       <c r="B4" t="n">
-        <v>80201</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lovarso Skrovellav 2, Dlr</t>
+          <t>Lovarso Skrovellav 3, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467375</v>
+        <v>467424</v>
       </c>
       <c r="R4" t="n">
-        <v>6821924</v>
+        <v>6821964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
         <v>129790542</v>
       </c>
       <c r="B5" t="n">
-        <v>80228</v>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129790558</v>
+        <v>129790637</v>
       </c>
       <c r="B6" t="n">
-        <v>80201</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lovarso Skrovellav 3, Dlr</t>
+          <t>Lovarso Talltita, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467424</v>
+        <v>467405</v>
       </c>
       <c r="R6" t="n">
-        <v>6821964</v>
+        <v>6822149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,6 +1191,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre sumpig granskog vid Lovarsuonjoki (k-skog)</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1189,21 +1204,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
